--- a/data/trans_dic/IQ23_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IQ23_R-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que duermen las horas recomendadas en función de su edad</t>
+          <t>Menores que duermen las horas recomendadas en función de su edad (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44,67; 60,59</t>
+          <t>45,11; 60,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>40,75; 55,4</t>
+          <t>41,07; 54,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41,18; 55,62</t>
+          <t>41,59; 54,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,43; 32,65</t>
+          <t>16,07; 32,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,09; 57,58</t>
+          <t>42,79; 56,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,84; 57,26</t>
+          <t>43,03; 57,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,31; 52,7</t>
+          <t>38,57; 52,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,95; 36,87</t>
+          <t>19,92; 37,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>46,19; 56,7</t>
+          <t>45,78; 56,32</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44,65; 54,15</t>
+          <t>44,58; 54,35</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41,45; 51,65</t>
+          <t>42,07; 52,11</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,19; 31,99</t>
+          <t>19,97; 32,17</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>71,05; 79,89</t>
+          <t>70,94; 79,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>69,47; 78,76</t>
+          <t>69,69; 78,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62,25; 72,26</t>
+          <t>62,39; 72,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58,13; 70,18</t>
+          <t>57,23; 70,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>74,34; 82,49</t>
+          <t>74,04; 82,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,68; 77,74</t>
+          <t>68,59; 77,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,48; 65,44</t>
+          <t>56,36; 66,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>57,93; 70,08</t>
+          <t>58,27; 70,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>73,88; 79,95</t>
+          <t>74,03; 79,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70,49; 77,02</t>
+          <t>70,54; 77,0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60,54; 67,47</t>
+          <t>59,95; 67,35</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>59,42; 68,29</t>
+          <t>59,67; 68,58</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72,72; 84,29</t>
+          <t>72,17; 84,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>73,11; 83,68</t>
+          <t>72,79; 83,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,79; 77,65</t>
+          <t>66,71; 77,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69,15; 81,02</t>
+          <t>69,12; 81,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>67,42; 79,21</t>
+          <t>67,62; 79,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68,02; 79,7</t>
+          <t>68,27; 80,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68,27; 78,94</t>
+          <t>68,11; 78,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>63,91; 76,04</t>
+          <t>63,79; 75,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>71,96; 79,76</t>
+          <t>71,81; 79,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>72,59; 80,56</t>
+          <t>72,41; 80,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68,96; 76,35</t>
+          <t>69,42; 76,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>68,54; 76,86</t>
+          <t>67,98; 76,78</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>74,34; 84,05</t>
+          <t>74,45; 83,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>77,62; 87,59</t>
+          <t>77,59; 87,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,37; 86,22</t>
+          <t>76,73; 86,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77,3; 87,38</t>
+          <t>77,41; 87,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>77,55; 86,31</t>
+          <t>77,81; 86,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,87; 87,74</t>
+          <t>78,43; 87,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,58; 88,07</t>
+          <t>78,58; 88,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>75,8; 85,42</t>
+          <t>76,03; 85,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>77,38; 84,04</t>
+          <t>77,6; 83,95</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79,76; 86,61</t>
+          <t>79,83; 86,34</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78,75; 85,82</t>
+          <t>79,16; 86,04</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>78,3; 85,45</t>
+          <t>78,17; 85,35</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>71,17; 76,38</t>
+          <t>70,72; 76,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>69,15; 74,47</t>
+          <t>69,04; 74,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65,99; 71,6</t>
+          <t>65,99; 71,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68,0; 75,21</t>
+          <t>67,77; 75,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>71,33; 76,62</t>
+          <t>71,13; 76,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,73; 74,11</t>
+          <t>68,83; 74,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,18; 69,86</t>
+          <t>64,22; 69,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>66,64; 73,23</t>
+          <t>66,24; 72,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>71,97; 75,8</t>
+          <t>71,92; 75,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69,71; 73,46</t>
+          <t>69,93; 73,84</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65,75; 69,67</t>
+          <t>65,38; 69,51</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>67,74; 72,85</t>
+          <t>67,87; 72,87</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que duermen las horas recomendadas en función de su edad (tasa de respuesta: 99,43%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>55466</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>70904</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>62608</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13334</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>60014</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>72864</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>56425</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>17239</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>115481</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>143768</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>119033</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>30574</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>47697; 64003</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60277; 80339</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53800; 71123</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9170; 18588</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>51317; 68318</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>62532; 83482</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>47680; 64810</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>12238; 22856</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>103306; 127097</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>130202; 158738</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>106449; 131836</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>23664; 38120</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>190624</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>174836</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>140167</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>102084</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>198824</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>197155</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>157198</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>117454</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>389448</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>371992</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>297364</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>219538</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>178644; 200962</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>164102; 185631</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>129900; 151288</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>91164; 111810</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>187437; 208676</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>184506; 209350</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>145083; 171702</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>106379; 128417</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>373857; 403847</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>355835; 388432</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>279164; 313620</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>203998; 234453</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>98755</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>123108</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>136738</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>131626</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>104367</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>118208</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>137972</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>147672</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>203121</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>241316</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>274710</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>279298</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>90598; 105564</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>113827; 130584</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>126018; 146266</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>119627; 140710</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>95690; 112037</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>108262; 126856</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>127174; 147141</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>134525; 159333</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>191763; 213563</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>228060; 252688</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>260775; 288831</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>261015; 294800</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>152327</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>142103</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>141082</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>222441</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>169162</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>149728</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>142681</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>248007</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>321489</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>291831</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>283763</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>470448</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>142979; 160968</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>132946; 149284</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>132579; 149750</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>209181; 237180</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>159410; 176914</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>140616; 157046</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>133935; 150488</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>231963; 260951</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>308013; 333207</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>279889; 302745</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>271700; 295314</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>449713; 491027</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1535</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1497</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1418</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1282</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>497172</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>510951</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>480594</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>469486</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>532368</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>537955</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>494276</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>530373</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1029540</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1048906</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>974870</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>999859</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>477467; 514381</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>490168; 529356</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>461446; 500446</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>447035; 496594</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>511759; 550048</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>517703; 559539</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>474082; 515200</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>503401; 552053</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1003068; 1055854</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1022475; 1079630</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>939878; 999255</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>963471; 1034488</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IQ23_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IQ23_R-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45,11; 60,54</t>
+          <t>45,17; 60,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41,07; 54,74</t>
+          <t>41,91; 54,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41,59; 54,98</t>
+          <t>41,64; 55,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,07; 32,57</t>
+          <t>16,46; 32,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>42,79; 56,96</t>
+          <t>43,3; 56,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,03; 57,45</t>
+          <t>44,13; 57,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,57; 52,42</t>
+          <t>38,16; 52,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,92; 37,2</t>
+          <t>20,24; 37,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>45,78; 56,32</t>
+          <t>45,52; 56,3</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44,58; 54,35</t>
+          <t>44,85; 54,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42,07; 52,11</t>
+          <t>42,02; 51,84</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,97; 32,17</t>
+          <t>20,22; 32,18</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>70,94; 79,8</t>
+          <t>70,96; 79,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>69,69; 78,84</t>
+          <t>69,43; 79,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62,39; 72,66</t>
+          <t>61,32; 71,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57,23; 70,19</t>
+          <t>57,44; 69,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>74,04; 82,43</t>
+          <t>74,38; 82,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,59; 77,83</t>
+          <t>68,45; 77,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,36; 66,7</t>
+          <t>56,03; 66,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>58,27; 70,34</t>
+          <t>58,18; 70,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>74,03; 79,97</t>
+          <t>74,12; 80,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70,54; 77,0</t>
+          <t>70,4; 77,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59,95; 67,35</t>
+          <t>60,47; 67,19</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>59,67; 68,58</t>
+          <t>59,71; 68,33</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72,17; 84,1</t>
+          <t>72,13; 84,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>72,79; 83,51</t>
+          <t>72,58; 83,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,71; 77,43</t>
+          <t>66,99; 77,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69,12; 81,3</t>
+          <t>69,17; 81,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>67,62; 79,17</t>
+          <t>67,45; 79,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68,27; 80,0</t>
+          <t>68,47; 79,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68,11; 78,8</t>
+          <t>68,58; 79,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>63,79; 75,55</t>
+          <t>63,42; 75,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>71,81; 79,97</t>
+          <t>71,56; 80,06</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>72,41; 80,23</t>
+          <t>72,63; 80,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>69,42; 76,89</t>
+          <t>69,21; 76,61</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>67,98; 76,78</t>
+          <t>68,38; 77,0</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>74,45; 83,81</t>
+          <t>74,46; 83,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>77,59; 87,13</t>
+          <t>78,04; 87,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,73; 86,67</t>
+          <t>76,26; 86,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77,41; 87,77</t>
+          <t>77,39; 87,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>77,81; 86,35</t>
+          <t>78,27; 86,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,43; 87,59</t>
+          <t>78,49; 87,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,58; 88,29</t>
+          <t>78,31; 88,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>76,03; 85,53</t>
+          <t>75,73; 85,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>77,6; 83,95</t>
+          <t>77,73; 84,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79,83; 86,34</t>
+          <t>79,93; 86,32</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79,16; 86,04</t>
+          <t>79,08; 85,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>78,17; 85,35</t>
+          <t>77,74; 85,19</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>70,72; 76,19</t>
+          <t>70,92; 76,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>69,04; 74,56</t>
+          <t>69,23; 74,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65,99; 71,57</t>
+          <t>65,55; 71,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67,77; 75,28</t>
+          <t>67,89; 75,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>71,13; 76,45</t>
+          <t>71,44; 76,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,83; 74,39</t>
+          <t>68,73; 74,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,22; 69,79</t>
+          <t>64,03; 69,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>66,24; 72,64</t>
+          <t>66,35; 72,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>71,92; 75,71</t>
+          <t>71,91; 75,67</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69,93; 73,84</t>
+          <t>69,76; 73,73</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65,38; 69,51</t>
+          <t>65,79; 69,72</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>67,87; 72,87</t>
+          <t>68,15; 72,75</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>47697; 64003</t>
+          <t>47752; 64163</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>60277; 80339</t>
+          <t>61506; 80574</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53800; 71123</t>
+          <t>53865; 72097</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9170; 18588</t>
+          <t>9396; 18474</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>51317; 68318</t>
+          <t>51936; 68118</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>62532; 83482</t>
+          <t>64134; 83111</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47680; 64810</t>
+          <t>47183; 64813</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12238; 22856</t>
+          <t>12435; 23098</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>103306; 127097</t>
+          <t>102722; 127054</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>130202; 158738</t>
+          <t>130990; 157954</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>106449; 131836</t>
+          <t>106309; 131164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23664; 38120</t>
+          <t>23965; 38135</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>178644; 200962</t>
+          <t>178694; 201019</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>164102; 185631</t>
+          <t>163483; 186049</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>129900; 151288</t>
+          <t>127681; 149733</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>91164; 111810</t>
+          <t>91508; 110962</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>187437; 208676</t>
+          <t>188307; 208685</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>184506; 209350</t>
+          <t>184114; 208728</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>145083; 171702</t>
+          <t>144240; 170184</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>106379; 128417</t>
+          <t>106212; 128843</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>373857; 403847</t>
+          <t>374315; 404145</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>355835; 388432</t>
+          <t>355121; 388520</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>279164; 313620</t>
+          <t>281584; 312889</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>203998; 234453</t>
+          <t>204117; 233587</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>90598; 105564</t>
+          <t>90545; 105990</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>113827; 130584</t>
+          <t>113489; 130857</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>126018; 146266</t>
+          <t>126551; 146563</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>119627; 140710</t>
+          <t>119715; 141193</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>95690; 112037</t>
+          <t>95446; 112537</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>108262; 126856</t>
+          <t>108571; 126155</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>127174; 147141</t>
+          <t>128060; 148130</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>134525; 159333</t>
+          <t>133740; 159977</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>191763; 213563</t>
+          <t>191094; 213794</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>228060; 252688</t>
+          <t>228726; 252142</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>260775; 288831</t>
+          <t>259956; 287781</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>261015; 294800</t>
+          <t>262541; 295641</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>142979; 160968</t>
+          <t>142999; 160747</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>132946; 149284</t>
+          <t>133715; 150270</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>132579; 149750</t>
+          <t>131755; 148868</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>209181; 237180</t>
+          <t>209121; 237476</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>159410; 176914</t>
+          <t>160350; 176837</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>140616; 157046</t>
+          <t>140722; 156360</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>133935; 150488</t>
+          <t>133486; 150264</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>231963; 260951</t>
+          <t>231030; 262154</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>308013; 333207</t>
+          <t>308544; 334433</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>279889; 302745</t>
+          <t>280236; 302652</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>271700; 295314</t>
+          <t>271427; 294184</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>449713; 491027</t>
+          <t>447259; 490104</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>477467; 514381</t>
+          <t>478826; 515681</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>490168; 529356</t>
+          <t>491483; 531483</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>461446; 500446</t>
+          <t>458336; 497620</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>447035; 496594</t>
+          <t>447861; 495758</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>511759; 550048</t>
+          <t>513998; 550329</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>517703; 559539</t>
+          <t>516931; 557348</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>474082; 515200</t>
+          <t>472693; 515355</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>503401; 552053</t>
+          <t>504217; 554632</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1003068; 1055854</t>
+          <t>1002908; 1055340</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1022475; 1079630</t>
+          <t>1019954; 1078025</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>939878; 999255</t>
+          <t>945678; 1002204</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>963471; 1034488</t>
+          <t>967512; 1032773</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IQ23_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IQ23_R-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>50,04%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>50,14%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>45,64%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>30,02%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>52,46%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>48,31%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>48,4%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>23,37%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>50,04%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>50,14%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>45,64%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,27%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45,17; 60,69</t>
+          <t>43,09; 57,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41,91; 54,9</t>
+          <t>42,84; 57,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41,64; 55,73</t>
+          <t>38,31; 52,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,46; 32,37</t>
+          <t>21,55; 39,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,3; 56,79</t>
+          <t>44,67; 60,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,13; 57,19</t>
+          <t>40,75; 55,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,16; 52,42</t>
+          <t>41,18; 55,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,24; 37,59</t>
+          <t>15,86; 32,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>45,52; 56,3</t>
+          <t>46,19; 56,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44,85; 54,08</t>
+          <t>44,65; 54,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42,02; 51,84</t>
+          <t>41,45; 51,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,22; 32,18</t>
+          <t>20,58; 32,31</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>78,54%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>73,29%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>61,06%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>66,02%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>75,7%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>74,25%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>67,32%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>64,08%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>78,54%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>73,29%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>61,06%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>65,54%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>70,96; 79,82</t>
+          <t>74,34; 82,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>69,43; 79,01</t>
+          <t>68,68; 77,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61,32; 71,91</t>
+          <t>55,48; 65,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57,44; 69,66</t>
+          <t>59,4; 71,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>74,38; 82,43</t>
+          <t>71,05; 79,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,45; 77,6</t>
+          <t>69,47; 78,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,03; 66,11</t>
+          <t>62,25; 72,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>58,18; 70,58</t>
+          <t>59,2; 70,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>74,12; 80,03</t>
+          <t>73,88; 79,95</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70,4; 77,02</t>
+          <t>70,49; 77,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60,47; 67,19</t>
+          <t>60,54; 67,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>59,71; 68,33</t>
+          <t>60,99; 69,54</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>73,75%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>74,55%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>73,89%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>70,28%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>78,67%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>78,73%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>72,39%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>76,05%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>73,75%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>74,55%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>73,89%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>73,49%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72,13; 84,43</t>
+          <t>67,42; 79,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>72,58; 83,69</t>
+          <t>68,02; 79,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,99; 77,59</t>
+          <t>68,27; 78,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69,17; 81,58</t>
+          <t>64,48; 76,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>67,45; 79,52</t>
+          <t>72,72; 84,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>68,47; 79,56</t>
+          <t>73,11; 83,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68,58; 79,33</t>
+          <t>66,79; 77,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>63,42; 75,86</t>
+          <t>70,69; 82,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>71,56; 80,06</t>
+          <t>71,96; 79,76</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>72,63; 80,06</t>
+          <t>72,59; 80,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>69,21; 76,61</t>
+          <t>68,96; 76,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>68,38; 77,0</t>
+          <t>69,19; 77,23</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>82,57%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>83,51%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>83,71%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>81,18%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>79,31%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>82,94%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>81,66%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>82,32%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>82,57%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>83,51%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>83,71%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>80,73%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>74,46; 83,7</t>
+          <t>77,55; 86,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,04; 87,7</t>
+          <t>78,87; 87,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,26; 86,16</t>
+          <t>78,58; 88,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77,39; 87,88</t>
+          <t>75,56; 85,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>78,27; 86,32</t>
+          <t>74,34; 84,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,49; 87,21</t>
+          <t>77,62; 87,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,31; 88,16</t>
+          <t>76,37; 86,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>75,73; 85,93</t>
+          <t>75,46; 84,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>77,73; 84,26</t>
+          <t>77,38; 84,04</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79,93; 86,32</t>
+          <t>79,76; 86,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79,08; 85,71</t>
+          <t>78,75; 85,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77,74; 85,19</t>
+          <t>77,36; 84,12</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>73,99%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>71,52%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>66,95%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70,97%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>73,64%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>71,97%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>68,73%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>71,17%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>73,99%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>71,52%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>66,95%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,99%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>70,92; 76,38</t>
+          <t>71,33; 76,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>69,23; 74,86</t>
+          <t>68,73; 74,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65,55; 71,16</t>
+          <t>64,18; 69,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67,89; 75,15</t>
+          <t>67,79; 74,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>71,44; 76,49</t>
+          <t>71,17; 76,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,73; 74,1</t>
+          <t>69,15; 74,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,03; 69,81</t>
+          <t>65,99; 71,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>66,35; 72,98</t>
+          <t>68,09; 73,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>71,91; 75,67</t>
+          <t>71,97; 75,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69,76; 73,73</t>
+          <t>69,71; 73,46</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65,79; 69,72</t>
+          <t>65,75; 69,67</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>68,15; 72,75</t>
+          <t>68,42; 73,08</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>60014</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>72864</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>56425</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>15171</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>55466</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>70904</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>62608</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13334</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>60014</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>72864</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>56425</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17239</t>
+          <t>11693</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30574</t>
+          <t>26864</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>47752; 64163</t>
+          <t>51677; 69065</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>61506; 80574</t>
+          <t>62261; 83204</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53865; 72097</t>
+          <t>47360; 65151</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9396; 18474</t>
+          <t>10891; 19816</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>51936; 68118</t>
+          <t>47222; 64062</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>64134; 83111</t>
+          <t>59805; 81309</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47183; 64813</t>
+          <t>53279; 71958</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12435; 23098</t>
+          <t>8207; 16634</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>102722; 127054</t>
+          <t>104223; 127955</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>130990; 157954</t>
+          <t>130425; 158170</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>106309; 131164</t>
+          <t>104862; 130679</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23965; 38135</t>
+          <t>21044; 33043</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>283</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>252</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>158</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>198824</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>197155</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>157198</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>103993</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>190624</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>174836</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>140167</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>102084</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>198824</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>197155</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>157198</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>117454</t>
+          <t>94618</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>219538</t>
+          <t>198611</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>178694; 201019</t>
+          <t>188192; 208822</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>163483; 186049</t>
+          <t>184732; 209118</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>127681; 149733</t>
+          <t>142831; 168474</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>91508; 110962</t>
+          <t>93565; 112803</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>188307; 208685</t>
+          <t>178931; 201197</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>184114; 208728</t>
+          <t>163567; 185446</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>144240; 170184</t>
+          <t>129614; 150455</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>106212; 128843</t>
+          <t>86142; 103014</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>374315; 404145</t>
+          <t>373065; 403738</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>355121; 388520</t>
+          <t>355582; 388552</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>281584; 312889</t>
+          <t>281917; 314180</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>204117; 233587</t>
+          <t>184813; 210747</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>174</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>197</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>179</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>104367</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>118208</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>137972</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>139529</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>98755</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>123108</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>136738</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>131626</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>104367</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>118208</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>137972</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>147672</t>
+          <t>134722</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>279298</t>
+          <t>274251</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>90545; 105990</t>
+          <t>95406; 112099</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>113489; 130857</t>
+          <t>107859; 126379</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>126551; 146563</t>
+          <t>127485; 147395</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>119715; 141193</t>
+          <t>127997; 151069</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>95446; 112537</t>
+          <t>91279; 105814</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>108571; 126155</t>
+          <t>114328; 130843</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>128060; 148130</t>
+          <t>126158; 146687</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>133740; 159977</t>
+          <t>123469; 143301</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>191094; 213794</t>
+          <t>192173; 213007</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>228726; 252142</t>
+          <t>228602; 253716</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>259956; 287781</t>
+          <t>259034; 286793</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>262541; 295641</t>
+          <t>258199; 288234</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>202</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>265</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>278</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>169162</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>149728</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>142681</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>237338</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>152327</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>142103</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>141082</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>222441</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>169162</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>149728</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>142681</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>248007</t>
+          <t>201701</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>470448</t>
+          <t>439039</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>142999; 160747</t>
+          <t>158885; 176826</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>133715; 150270</t>
+          <t>141402; 157299</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>131755; 148868</t>
+          <t>133932; 150123</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>209121; 237476</t>
+          <t>220907; 249512</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>160350; 176837</t>
+          <t>142776; 161432</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>140722; 156360</t>
+          <t>132985; 150080</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>133486; 150264</t>
+          <t>131943; 148975</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>231030; 262154</t>
+          <t>189759; 211535</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>308544; 334433</t>
+          <t>307156; 333579</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>280236; 302652</t>
+          <t>279666; 303689</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>271427; 294184</t>
+          <t>270305; 294562</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>447259; 490104</t>
+          <t>420685; 457466</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>737</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>731</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>716</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>630</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>798</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>766</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>532368</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>537955</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>494276</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>496031</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>497172</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>510951</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>480594</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>469486</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>532368</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>537955</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>494276</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>530373</t>
+          <t>442733</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>999859</t>
+          <t>938765</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>478826; 515681</t>
+          <t>513235; 551237</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>491483; 531483</t>
+          <t>516946; 557406</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>458336; 497620</t>
+          <t>473777; 515717</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>447861; 495758</t>
+          <t>473783; 518880</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>513998; 550329</t>
+          <t>480522; 515664</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>516931; 557348</t>
+          <t>490900; 528676</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>472693; 515355</t>
+          <t>461458; 500683</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>504217; 554632</t>
+          <t>424474; 460390</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1002908; 1055340</t>
+          <t>1003723; 1057093</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1019954; 1078025</t>
+          <t>1019157; 1074094</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>945678; 1002204</t>
+          <t>945109; 1001563</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>967512; 1032773</t>
+          <t>904712; 966284</t>
         </is>
       </c>
     </row>
